--- a/experiment_results/combined_sweep/rtt_bursts_S3_atk5pct_wu500000.xlsx
+++ b/experiment_results/combined_sweep/rtt_bursts_S3_atk5pct_wu500000.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -548,12 +548,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -605,12 +605,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>469427</t>
+          <t>248989</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -662,12 +662,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>497701</t>
+          <t>248736</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -719,12 +719,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>500793</t>
+          <t>252081</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -776,12 +776,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>516049</t>
+          <t>263992</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -833,7 +833,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>539131</t>
+          <t>275163</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>621372</t>
+          <t>346233</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>711065</t>
+          <t>364856</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>753614</t>
+          <t>388781</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1061,12 +1061,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>792765</t>
+          <t>404008</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1118,12 +1118,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>827659</t>
+          <t>423675</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1175,12 +1175,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>870841</t>
+          <t>447190</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>909334</t>
+          <t>462168</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1289,12 +1289,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>941623</t>
+          <t>479478</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1346,12 +1346,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>950789</t>
+          <t>471335</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1403,12 +1403,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>931867</t>
+          <t>460557</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1460,12 +1460,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>921130</t>
+          <t>460597</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
